--- a/segments/共通マスタ・周辺_セグメント見積.xlsx
+++ b/segments/共通マスタ・周辺_セグメント見積.xlsx
@@ -1291,10 +1291,8 @@
           <t>経済安保対象（ODC除外）</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
+      <c r="C7" s="7" t="n">
+        <v>113.35</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -1964,17 +1962,20 @@
           <t>原価_国内（百万円）</t>
         </is>
       </c>
-      <c r="C46" s="23">
-        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C26+試算条件!C27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34),$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*(1-試算条件!C20))</f>
-        <v/>
-      </c>
-      <c r="D46" s="23">
-        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D26+試算条件!D27))*(試算条件!D$33*試算条件!D$35+(1-試算条件!D$33)*試算条件!D$34),$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D30)*(1-(試算条件!D26+試算条件!D27))*(1-試算条件!D20))</f>
-        <v/>
-      </c>
-      <c r="E46" s="23">
-        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E26+試算条件!E27))*(試算条件!E$33*試算条件!E$35+(1-試算条件!E$33)*試算条件!E$34),$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E30)*(1-(試算条件!E26+試算条件!E27))*(1-試算条件!E20))</f>
-        <v/>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C26+試算条件!C27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!C20),$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*(1-試算条件!C20))</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D26+試算条件!D27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!D20),$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C30)*(1-(試算条件!D26+試算条件!D27))*(1-試算条件!D20))</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E26+試算条件!E27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!E20),$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C30)*(1-(試算条件!E26+試算条件!E27))*(1-試算条件!E20))</t>
+        </is>
       </c>
       <c r="F46" s="22">
         <f>SUM(C46:E46)</f>
@@ -1987,17 +1988,20 @@
           <t>原価_ODC（百万円）</t>
         </is>
       </c>
-      <c r="C47" s="23">
-        <f>IF($C$6="②COB白地",0,$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*試算条件!C20*試算条件!C21)</f>
-        <v/>
-      </c>
-      <c r="D47" s="23">
-        <f>IF($C$6="②COB白地",0,$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D30)*(1-(試算条件!D26+試算条件!D27))*試算条件!D20*試算条件!D21)</f>
-        <v/>
-      </c>
-      <c r="E47" s="23">
-        <f>IF($C$6="②COB白地",0,$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E30)*(1-(試算条件!E26+試算条件!E27))*試算条件!E20*試算条件!E21)</f>
-        <v/>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C26+試算条件!C27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!C20*試算条件!C21,$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*試算条件!C20*試算条件!C21)</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D26+試算条件!D27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!D20*試算条件!D21,$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C30)*(1-(試算条件!D26+試算条件!D27))*試算条件!D20*試算条件!D21)</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E26+試算条件!E27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!E20*試算条件!E21,$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C30)*(1-(試算条件!E26+試算条件!E27))*試算条件!E20*試算条件!E21)</t>
+        </is>
       </c>
       <c r="F47" s="22">
         <f>SUM(C47:E47)</f>
@@ -2206,17 +2210,20 @@
           <t>原価_国内（百万円）</t>
         </is>
       </c>
-      <c r="C58" s="23">
-        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C28+試算条件!C29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34),$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*(1-試算条件!C20))</f>
-        <v/>
-      </c>
-      <c r="D58" s="23">
-        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D28+試算条件!D29))*(試算条件!D$33*試算条件!D$35+(1-試算条件!D$33)*試算条件!D$34),$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D31)*(1-(試算条件!D28+試算条件!D29))*(1-試算条件!D20))</f>
-        <v/>
-      </c>
-      <c r="E58" s="23">
-        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E28+試算条件!E29))*(試算条件!E$33*試算条件!E$35+(1-試算条件!E$33)*試算条件!E$34),$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E31)*(1-(試算条件!E28+試算条件!E29))*(1-試算条件!E20))</f>
-        <v/>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C28+試算条件!C29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!C20),$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*(1-試算条件!C20))</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D28+試算条件!D29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!D20),$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C31)*(1-(試算条件!D28+試算条件!D29))*(1-試算条件!D20))</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E28+試算条件!E29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!E20),$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C31)*(1-(試算条件!E28+試算条件!E29))*(1-試算条件!E20))</t>
+        </is>
       </c>
       <c r="F58" s="22">
         <f>SUM(C58:E58)</f>
@@ -2229,17 +2236,20 @@
           <t>原価_ODC（百万円）</t>
         </is>
       </c>
-      <c r="C59" s="23">
-        <f>IF($C$6="②COB白地",0,$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*試算条件!C20*試算条件!C21)</f>
-        <v/>
-      </c>
-      <c r="D59" s="23">
-        <f>IF($C$6="②COB白地",0,$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D31)*(1-(試算条件!D28+試算条件!D29))*試算条件!D20*試算条件!D21)</f>
-        <v/>
-      </c>
-      <c r="E59" s="23">
-        <f>IF($C$6="②COB白地",0,$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E31)*(1-(試算条件!E28+試算条件!E29))*試算条件!E20*試算条件!E21)</f>
-        <v/>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C28+試算条件!C29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!C20*試算条件!C21,$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*試算条件!C20*試算条件!C21)</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D28+試算条件!D29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!D20*試算条件!D21,$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C31)*(1-(試算条件!D28+試算条件!D29))*試算条件!D20*試算条件!D21)</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E28+試算条件!E29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!E20*試算条件!E21,$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C31)*(1-(試算条件!E28+試算条件!E29))*試算条件!E20*試算条件!E21)</t>
+        </is>
       </c>
       <c r="F59" s="22">
         <f>SUM(C59:E59)</f>

--- a/segments/共通マスタ・周辺_セグメント見積.xlsx
+++ b/segments/共通マスタ・周辺_セグメント見積.xlsx
@@ -1962,20 +1962,17 @@
           <t>原価_国内（百万円）</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C26+試算条件!C27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!C20),$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*(1-試算条件!C20))</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D26+試算条件!D27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!D20),$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C30)*(1-(試算条件!D26+試算条件!D27))*(1-試算条件!D20))</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E26+試算条件!E27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!E20),$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C30)*(1-(試算条件!E26+試算条件!E27))*(1-試算条件!E20))</t>
-        </is>
+      <c r="C46" s="23">
+        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C26+試算条件!C27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!C20),$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*(1-試算条件!C20))</f>
+        <v/>
+      </c>
+      <c r="D46" s="23">
+        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D26+試算条件!D27))*(試算条件!D$33*試算条件!D$35+(1-試算条件!D$33)*試算条件!D$34)*(1-試算条件!D20),$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D30)*(1-(試算条件!D26+試算条件!D27))*(1-試算条件!D20))</f>
+        <v/>
+      </c>
+      <c r="E46" s="23">
+        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E26+試算条件!E27))*(試算条件!E$33*試算条件!E$35+(1-試算条件!E$33)*試算条件!E$34)*(1-試算条件!E20),$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E30)*(1-(試算条件!E26+試算条件!E27))*(1-試算条件!E20))</f>
+        <v/>
       </c>
       <c r="F46" s="22">
         <f>SUM(C46:E46)</f>
@@ -1988,20 +1985,17 @@
           <t>原価_ODC（百万円）</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C26+試算条件!C27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!C20*試算条件!C21,$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*試算条件!C20*試算条件!C21)</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D26+試算条件!D27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!D20*試算条件!D21,$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C30)*(1-(試算条件!D26+試算条件!D27))*試算条件!D20*試算条件!D21)</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E26+試算条件!E27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!E20*試算条件!E21,$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C30)*(1-(試算条件!E26+試算条件!E27))*試算条件!E20*試算条件!E21)</t>
-        </is>
+      <c r="C47" s="23">
+        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C26+試算条件!C27))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!C20*試算条件!C21,$C$8*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C30)*(1-(試算条件!C26+試算条件!C27))*試算条件!C20*試算条件!C21)</f>
+        <v/>
+      </c>
+      <c r="D47" s="23">
+        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D26+試算条件!D27))*(試算条件!D$33*試算条件!D$35+(1-試算条件!D$33)*試算条件!D$34)*試算条件!D20*試算条件!D21,$C$8*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D30)*(1-(試算条件!D26+試算条件!D27))*試算条件!D20*試算条件!D21)</f>
+        <v/>
+      </c>
+      <c r="E47" s="23">
+        <f>IF($C$6="②COB白地",$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E26+試算条件!E27))*(試算条件!E$33*試算条件!E$35+(1-試算条件!E$33)*試算条件!E$34)*試算条件!E20*試算条件!E21,$C$8*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E30)*(1-(試算条件!E26+試算条件!E27))*試算条件!E20*試算条件!E21)</f>
+        <v/>
       </c>
       <c r="F47" s="22">
         <f>SUM(C47:E47)</f>
@@ -2210,20 +2204,17 @@
           <t>原価_国内（百万円）</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C28+試算条件!C29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!C20),$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*(1-試算条件!C20))</t>
-        </is>
-      </c>
-      <c r="D58" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D28+試算条件!D29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!D20),$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C31)*(1-(試算条件!D28+試算条件!D29))*(1-試算条件!D20))</t>
-        </is>
-      </c>
-      <c r="E58" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E28+試算条件!E29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!E20),$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C31)*(1-(試算条件!E28+試算条件!E29))*(1-試算条件!E20))</t>
-        </is>
+      <c r="C58" s="23">
+        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C28+試算条件!C29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*(1-試算条件!C20),$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*(1-試算条件!C20))</f>
+        <v/>
+      </c>
+      <c r="D58" s="23">
+        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D28+試算条件!D29))*(試算条件!D$33*試算条件!D$35+(1-試算条件!D$33)*試算条件!D$34)*(1-試算条件!D20),$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D31)*(1-(試算条件!D28+試算条件!D29))*(1-試算条件!D20))</f>
+        <v/>
+      </c>
+      <c r="E58" s="23">
+        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E28+試算条件!E29))*(試算条件!E$33*試算条件!E$35+(1-試算条件!E$33)*試算条件!E$34)*(1-試算条件!E20),$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E31)*(1-(試算条件!E28+試算条件!E29))*(1-試算条件!E20))</f>
+        <v/>
       </c>
       <c r="F58" s="22">
         <f>SUM(C58:E58)</f>
@@ -2236,20 +2227,17 @@
           <t>原価_ODC（百万円）</t>
         </is>
       </c>
-      <c r="C59" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C28+試算条件!C29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!C20*試算条件!C21,$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*試算条件!C20*試算条件!C21)</t>
-        </is>
-      </c>
-      <c r="D59" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D28+試算条件!D29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!D20*試算条件!D21,$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!C31)*(1-(試算条件!D28+試算条件!D29))*試算条件!D20*試算条件!D21)</t>
-        </is>
-      </c>
-      <c r="E59" s="23" t="inlineStr">
-        <is>
-          <t>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E28+試算条件!E29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!E20*試算条件!E21,$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!C31)*(1-(試算条件!E28+試算条件!E29))*試算条件!E20*試算条件!E21)</t>
-        </is>
+      <c r="C59" s="23">
+        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-(試算条件!C28+試算条件!C29))*(試算条件!C$33*試算条件!C$35+(1-試算条件!C$33)*試算条件!C$34)*試算条件!C20*試算条件!C21,$C$9*100*(1-試算条件!$C$10)*試算条件!C17*(1-試算条件!C31)*(1-(試算条件!C28+試算条件!C29))*試算条件!C20*試算条件!C21)</f>
+        <v/>
+      </c>
+      <c r="D59" s="23">
+        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-(試算条件!D28+試算条件!D29))*(試算条件!D$33*試算条件!D$35+(1-試算条件!D$33)*試算条件!D$34)*試算条件!D20*試算条件!D21,$C$9*100*(1-試算条件!$C$10)*試算条件!D17*(1-試算条件!D31)*(1-(試算条件!D28+試算条件!D29))*試算条件!D20*試算条件!D21)</f>
+        <v/>
+      </c>
+      <c r="E59" s="23">
+        <f>IF($C$6="②COB白地",$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-(試算条件!E28+試算条件!E29))*(試算条件!E$33*試算条件!E$35+(1-試算条件!E$33)*試算条件!E$34)*試算条件!E20*試算条件!E21,$C$9*100*(1-試算条件!$C$10)*試算条件!E17*(1-試算条件!E31)*(1-(試算条件!E28+試算条件!E29))*試算条件!E20*試算条件!E21)</f>
+        <v/>
       </c>
       <c r="F59" s="22">
         <f>SUM(C59:E59)</f>
